--- a/docs/CodeSystem-data-type.xlsx
+++ b/docs/CodeSystem-data-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T16:34:58+00:00</t>
+    <t>2026-02-20T16:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-data-type.xlsx
+++ b/docs/CodeSystem-data-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T16:31:02+00:00</t>
+    <t>2026-03-05T20:27:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-data-type.xlsx
+++ b/docs/CodeSystem-data-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T20:27:55+00:00</t>
+    <t>2026-03-10T20:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-data-type.xlsx
+++ b/docs/CodeSystem-data-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="71">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T20:40:46+00:00</t>
+    <t>2026-03-24T15:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>10</t>
+    <t>15</t>
   </si>
   <si>
     <t>Level</t>
@@ -141,55 +141,91 @@
     <t>1</t>
   </si>
   <si>
-    <t>Unaligned-Reads</t>
-  </si>
-  <si>
-    <t>Unaligned Reads</t>
-  </si>
-  <si>
-    <t>Aligned-reads</t>
+    <t>Raw-Sequencing-Reads</t>
+  </si>
+  <si>
+    <t>Raw Sequencing Reads</t>
+  </si>
+  <si>
+    <t>Raw-Sequencing-Reads-R1</t>
+  </si>
+  <si>
+    <t>Raw Sequencing Reads R1</t>
+  </si>
+  <si>
+    <t>Raw-Sequencing-Reads-R2</t>
+  </si>
+  <si>
+    <t>Raw Sequencing Reads R2</t>
+  </si>
+  <si>
+    <t>Aligned-Reads</t>
   </si>
   <si>
     <t>Aligned Reads</t>
   </si>
   <si>
+    <t>Aligned-Reads-Index</t>
+  </si>
+  <si>
+    <t>Aligned Reads Index</t>
+  </si>
+  <si>
     <t>SNV</t>
   </si>
   <si>
-    <t>Germline-CNV</t>
-  </si>
-  <si>
-    <t>Germline CNV</t>
-  </si>
-  <si>
-    <t>Sequencing-data-supplement</t>
-  </si>
-  <si>
-    <t>Supplement</t>
-  </si>
-  <si>
-    <t>Metrics</t>
-  </si>
-  <si>
-    <t>Sequencing-data-index</t>
-  </si>
-  <si>
-    <t>Sequencing Data Index</t>
-  </si>
-  <si>
-    <t>Germline-structural-variant</t>
-  </si>
-  <si>
-    <t>Germline Structural Variant</t>
+    <t>Single Nucleotide Variants (SNVs)</t>
+  </si>
+  <si>
+    <t>InDel</t>
+  </si>
+  <si>
+    <t>Insertions and Deletions (InDels)</t>
+  </si>
+  <si>
+    <t>SV</t>
+  </si>
+  <si>
+    <t>Structural Variations (SVs)</t>
+  </si>
+  <si>
+    <t>CNV</t>
+  </si>
+  <si>
+    <t>Copy Number Variations (CNVs)</t>
+  </si>
+  <si>
+    <t>Variant-Calls-Index</t>
+  </si>
+  <si>
+    <t>Variant Calls Index</t>
+  </si>
+  <si>
+    <t>Joint-Genotype-SNV</t>
+  </si>
+  <si>
+    <t>Joint Genotype SNV</t>
+  </si>
+  <si>
+    <t>Annotated-SNV</t>
+  </si>
+  <si>
+    <t>Annotated SNV</t>
+  </si>
+  <si>
+    <t>Quality-Control-Metrics</t>
+  </si>
+  <si>
+    <t>Quality Control Metrics</t>
+  </si>
+  <si>
+    <t>Sequencing-Data-Supplement</t>
+  </si>
+  <si>
+    <t>Sequencing Data Supplement</t>
   </si>
   <si>
     <t>IGV</t>
-  </si>
-  <si>
-    <t>Annotated-SNV</t>
-  </si>
-  <si>
-    <t>Annotated SNV</t>
   </si>
 </sst>
 </file>
@@ -499,7 +535,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -548,7 +584,7 @@
         <v>46</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -557,10 +593,10 @@
         <v>41</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -569,10 +605,10 @@
         <v>41</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -581,10 +617,10 @@
         <v>41</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -593,10 +629,10 @@
         <v>41</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -605,10 +641,10 @@
         <v>41</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -617,10 +653,10 @@
         <v>41</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -629,12 +665,72 @@
         <v>41</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="D16" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/docs/CodeSystem-data-type.xlsx
+++ b/docs/CodeSystem-data-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:55:50+00:00</t>
+    <t>2026-04-08T14:48:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-data-type.xlsx
+++ b/docs/CodeSystem-data-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:48:38+00:00</t>
+    <t>2026-04-10T13:54:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-data-type.xlsx
+++ b/docs/CodeSystem-data-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="73">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:54:16+00:00</t>
+    <t>2026-04-21T17:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>Level</t>
@@ -226,6 +226,12 @@
   </si>
   <si>
     <t>IGV</t>
+  </si>
+  <si>
+    <t>Laboratory-Values</t>
+  </si>
+  <si>
+    <t>Laboratory Values</t>
   </si>
 </sst>
 </file>
@@ -535,7 +541,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -732,6 +738,18 @@
       </c>
       <c r="D16" s="2"/>
     </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/CodeSystem-data-type.xlsx
+++ b/docs/CodeSystem-data-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:45:58+00:00</t>
+    <t>2026-06-08T17:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-data-type.xlsx
+++ b/docs/CodeSystem-data-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="114">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T17:19:56+00:00</t>
+    <t>2026-08-05T14:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>16</t>
+    <t>37</t>
   </si>
   <si>
     <t>Level</t>
@@ -147,6 +147,12 @@
     <t>Raw Sequencing Reads</t>
   </si>
   <si>
+    <t>Unaligned-Reads-Index</t>
+  </si>
+  <si>
+    <t>Unaligned Reads Index</t>
+  </si>
+  <si>
     <t>Raw-Sequencing-Reads-R1</t>
   </si>
   <si>
@@ -232,6 +238,123 @@
   </si>
   <si>
     <t>Laboratory Values</t>
+  </si>
+  <si>
+    <t>Raw-Sequencing-Reads-I1</t>
+  </si>
+  <si>
+    <t>Raw Sequencing Reads I1</t>
+  </si>
+  <si>
+    <t>Raw-Sequencing-Reads-I2</t>
+  </si>
+  <si>
+    <t>Raw Sequencing Reads I2</t>
+  </si>
+  <si>
+    <t>Processed-Reads</t>
+  </si>
+  <si>
+    <t>Processed Reads</t>
+  </si>
+  <si>
+    <t>Processed-Reads-Index</t>
+  </si>
+  <si>
+    <t>Processed Reads Index</t>
+  </si>
+  <si>
+    <t>De-Novo-Assembly-Aligned-Reads</t>
+  </si>
+  <si>
+    <t>De Novo Assembly Aligned Reads</t>
+  </si>
+  <si>
+    <t>De-Novo-Assembly-Aligned-Reads-Index</t>
+  </si>
+  <si>
+    <t>De Novo Assembly Aligned Reads Index</t>
+  </si>
+  <si>
+    <t>Methylation-Calls</t>
+  </si>
+  <si>
+    <t>Methylation Calls</t>
+  </si>
+  <si>
+    <t>Methylation-Calls-Index</t>
+  </si>
+  <si>
+    <t>Methylation Calls Index</t>
+  </si>
+  <si>
+    <t>Raw-Feature-Count-Matrix</t>
+  </si>
+  <si>
+    <t>Raw Feature Count Matrix</t>
+  </si>
+  <si>
+    <t>Filtered-Feature-Count-Matrix</t>
+  </si>
+  <si>
+    <t>Filtered Feature Count Matrix</t>
+  </si>
+  <si>
+    <t>Raw-Peak-Barcode-Matrix</t>
+  </si>
+  <si>
+    <t>Raw Peak Barcode Matrix</t>
+  </si>
+  <si>
+    <t>Filtered-Peak-Barcode-Matrix</t>
+  </si>
+  <si>
+    <t>Filtered Peak Barcode Matrix</t>
+  </si>
+  <si>
+    <t>Peak-Calls</t>
+  </si>
+  <si>
+    <t>Peak Calls</t>
+  </si>
+  <si>
+    <t>Peak-Calls-Index</t>
+  </si>
+  <si>
+    <t>Peak Calls Index</t>
+  </si>
+  <si>
+    <t>Annotated-Peaks</t>
+  </si>
+  <si>
+    <t>Annotated Peaks</t>
+  </si>
+  <si>
+    <t>Tandem-Repeats</t>
+  </si>
+  <si>
+    <t>Tandem Repeats (TRs)</t>
+  </si>
+  <si>
+    <t>Secondary-Analysis</t>
+  </si>
+  <si>
+    <t>Secondary Analysis</t>
+  </si>
+  <si>
+    <t>Gene-Annotations</t>
+  </si>
+  <si>
+    <t>Gene Annotations</t>
+  </si>
+  <si>
+    <t>Pedigree</t>
+  </si>
+  <si>
+    <t>Psychiatric-Assessment-Scores</t>
+  </si>
+  <si>
+    <t>Psychiatric Assessment Scores</t>
   </si>
 </sst>
 </file>
@@ -541,7 +664,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -734,7 +857,7 @@
         <v>70</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" s="2"/>
     </row>
@@ -743,12 +866,264 @@
         <v>41</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>72</v>
       </c>
       <c r="D17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="D38" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
